--- a/artfynd/A 25752-2025 artfynd.xlsx
+++ b/artfynd/A 25752-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,218 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126017469</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78374</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Särnstugan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413585</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6827578</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126017470</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Särnstugan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>413630</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6827601</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25752-2025 artfynd.xlsx
+++ b/artfynd/A 25752-2025 artfynd.xlsx
@@ -1117,7 +1117,7 @@
         <v>126017470</v>
       </c>
       <c r="B6" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25752-2025 artfynd.xlsx
+++ b/artfynd/A 25752-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>126017469</v>
       </c>
       <c r="B5" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>126017470</v>
       </c>
       <c r="B6" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
